--- a/Docs/NUCLEO-F446RE+IHM07M1_MorphoPinMap_for_FOC.xlsx
+++ b/Docs/NUCLEO-F446RE+IHM07M1_MorphoPinMap_for_FOC.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Development\01_Source\Neurodyne\NRD-W300-V1\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52546BD5-BB13-4D97-AFAC-CEBDD1D6BACD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B3DB64-085B-4AC8-9D4E-88549A0BD535}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7920" xr2:uid="{3F33A97E-B7C8-4778-8269-6C22CB84549D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7920" activeTab="1" xr2:uid="{3F33A97E-B7C8-4778-8269-6C22CB84549D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="IHM07M1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="141">
   <si>
     <t>CN7</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -512,6 +513,82 @@
   </si>
   <si>
     <t>CAN1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable_CH1-L6230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable_CH2-L6230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable_CH3-L6230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO/DAC/PWM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encoder A/Hall H1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encoder/Hall PS voltage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blue Button</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potentiometer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encoder Z/Hall H3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CURRENT REF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAC_Ch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encoder B/Hall H2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature feedback</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,9 +661,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -597,6 +671,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -926,50 +1003,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="G2" s="2" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="G2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -978,20 +1055,20 @@
       <c r="E4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1000,20 +1077,20 @@
       <c r="E5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1022,10 +1099,10 @@
       <c r="E6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>3</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1036,36 +1113,36 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>4</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>5</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>40</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1076,144 +1153,144 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>6</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>7</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>8</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>43</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>9</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>9</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>10</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>10</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>11</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>11</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>12</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>12</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>45</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>13</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>13</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1224,18 +1301,18 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>14</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>14</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>47</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1246,18 +1323,18 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>15</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>15</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1268,28 +1345,28 @@
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>16</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>16</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>17</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1298,10 +1375,10 @@
       <c r="E20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>17</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>50</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1312,36 +1389,36 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>18</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>18</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>19</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>19</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -1352,28 +1429,28 @@
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>20</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>20</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>21</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1382,10 +1459,10 @@
       <c r="E24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>21</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -1396,18 +1473,18 @@
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>22</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>22</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1418,18 +1495,18 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>23</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>23</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="4" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1440,18 +1517,18 @@
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>24</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>24</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1462,18 +1539,18 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>25</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>25</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1484,46 +1561,46 @@
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>26</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>26</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="4" t="s">
         <v>63</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>27</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>27</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="4" t="s">
         <v>60</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>28</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1532,10 +1609,10 @@
       <c r="E31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>28</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="4" t="s">
         <v>59</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -1546,28 +1623,28 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>29</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>29</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="4" t="s">
         <v>58</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>30</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1576,28 +1653,28 @@
       <c r="E33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>30</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="4" t="s">
         <v>61</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>31</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>31</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="4" t="s">
         <v>62</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -1608,36 +1685,36 @@
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>32</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <v>32</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>33</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>33</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -1648,10 +1725,10 @@
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>34</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -1660,10 +1737,10 @@
       <c r="E37" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <v>34</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -1674,10 +1751,10 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>35</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -1686,20 +1763,20 @@
       <c r="E38" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <v>35</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="4" t="s">
         <v>66</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>36</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -1708,20 +1785,20 @@
       <c r="E39" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <v>36</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>37</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -1730,20 +1807,20 @@
       <c r="E40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="4">
         <v>37</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>38</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -1752,10 +1829,10 @@
       <c r="E41" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="4">
         <v>38</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="1"/>
@@ -1767,7 +1844,635 @@
     <mergeCell ref="G2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FCB597-D7D6-41D9-8BD8-AD3F02DE5BC5}">
+  <dimension ref="B2:N21"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="5.625" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="10" width="5.625" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="13" width="5.625" customWidth="1"/>
+    <col min="14" max="14" width="20.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="4">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <v>2</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="4">
+        <v>3</v>
+      </c>
+      <c r="M4" s="4">
+        <v>4</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="1"/>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="4">
+        <v>3</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="4">
+        <v>5</v>
+      </c>
+      <c r="M5" s="4">
+        <v>6</v>
+      </c>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="1"/>
+      <c r="C6" s="4">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="4">
+        <v>4</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="4">
+        <v>7</v>
+      </c>
+      <c r="M6" s="4">
+        <v>8</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="C7" s="4">
+        <v>9</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="4">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="4">
+        <v>9</v>
+      </c>
+      <c r="M7" s="4">
+        <v>10</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+      <c r="C8" s="4">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="4">
+        <v>6</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L8" s="4">
+        <v>11</v>
+      </c>
+      <c r="M8" s="4">
+        <v>12</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="C9" s="4">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="4">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="4">
+        <v>7</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="4">
+        <v>13</v>
+      </c>
+      <c r="M9" s="4">
+        <v>14</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="C10" s="4">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="4">
+        <v>8</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="4">
+        <v>15</v>
+      </c>
+      <c r="M10" s="4">
+        <v>16</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="4">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="4">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="4">
+        <v>9</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="4">
+        <v>17</v>
+      </c>
+      <c r="M11" s="4">
+        <v>18</v>
+      </c>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="C12" s="4">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="4">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="4">
+        <v>10</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="4">
+        <v>19</v>
+      </c>
+      <c r="M12" s="4">
+        <v>20</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="C13" s="4">
+        <v>21</v>
+      </c>
+      <c r="D13" s="4">
+        <v>22</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="4">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="4">
+        <v>21</v>
+      </c>
+      <c r="M13" s="4">
+        <v>22</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="4">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="4">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="4">
+        <v>23</v>
+      </c>
+      <c r="M14" s="4">
+        <v>24</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="C15" s="4">
+        <v>25</v>
+      </c>
+      <c r="D15" s="4">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="4">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L15" s="4">
+        <v>25</v>
+      </c>
+      <c r="M15" s="4">
+        <v>26</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="C16" s="4">
+        <v>27</v>
+      </c>
+      <c r="D16" s="4">
+        <v>28</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="4">
+        <v>3</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L16" s="4">
+        <v>27</v>
+      </c>
+      <c r="M16" s="4">
+        <v>28</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="C17" s="4">
+        <v>29</v>
+      </c>
+      <c r="D17" s="4">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="4">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="4">
+        <v>29</v>
+      </c>
+      <c r="M17" s="4">
+        <v>30</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="1"/>
+      <c r="C18" s="4">
+        <v>31</v>
+      </c>
+      <c r="D18" s="4">
+        <v>32</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="4">
+        <v>5</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L18" s="4">
+        <v>31</v>
+      </c>
+      <c r="M18" s="4">
+        <v>32</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="1"/>
+      <c r="C19" s="4">
+        <v>33</v>
+      </c>
+      <c r="D19" s="4">
+        <v>34</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="4">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="4">
+        <v>6</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="4">
+        <v>33</v>
+      </c>
+      <c r="M19" s="4">
+        <v>34</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="4">
+        <v>35</v>
+      </c>
+      <c r="D20" s="4">
+        <v>36</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="4">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="4">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="4">
+        <v>35</v>
+      </c>
+      <c r="M20" s="4">
+        <v>36</v>
+      </c>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4">
+        <v>37</v>
+      </c>
+      <c r="D21" s="4">
+        <v>38</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="4">
+        <v>6</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="4">
+        <v>8</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="4">
+        <v>37</v>
+      </c>
+      <c r="M21" s="4">
+        <v>38</v>
+      </c>
+      <c r="N21" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>